--- a/Cardiologie/Excel/cardio_3.xlsx
+++ b/Cardiologie/Excel/cardio_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D156F103-1420-478E-8BC2-55743EF7BDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B9CA25-E8D9-43C7-8F5C-23E8CD5377A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="404">
   <si>
     <t>L'angor stable est défini comme la survenue imprévisible d’une sensation d’oppression thoracique ou d’étouffement lors d’effort physiques ou d’émotions.</t>
   </si>
@@ -1160,6 +1160,78 @@
   </si>
   <si>
     <t>L’angine de poitrine asymptomatique est un indicateur de mauvais pronostic. 114 . VRAI</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>survenue prévisible</t>
+  </si>
+  <si>
+    <t>3-6 mois</t>
+  </si>
+  <si>
+    <t>moins de 5 min au repos</t>
+  </si>
+  <si>
+    <t>épicardique</t>
+  </si>
+  <si>
+    <t>5 à 8 fois</t>
+  </si>
+  <si>
+    <t>sévere</t>
+  </si>
+  <si>
+    <t>oui psk la survenue est prévisible</t>
+  </si>
+  <si>
+    <t>sont souvent asymptomatique</t>
+  </si>
+  <si>
+    <t>Nan c le matin</t>
+  </si>
+  <si>
+    <t>non c'est l'hyperthyroïdie</t>
+  </si>
+  <si>
+    <t>se base principalement sur le clinique</t>
+  </si>
+  <si>
+    <t>en diastole</t>
+  </si>
+  <si>
+    <t>c'est l'inverse</t>
+  </si>
+  <si>
+    <t>par un sous-décalage</t>
+  </si>
+  <si>
+    <t>normal chez la majorité des patients</t>
+  </si>
+  <si>
+    <t>contre indiqué si angor instable ou infarctus myocardique</t>
+  </si>
+  <si>
+    <t>si l'ECG au repos est anormale</t>
+  </si>
+  <si>
+    <t>à l'effort maximal</t>
+  </si>
+  <si>
+    <t>C'est un beta mimétique</t>
+  </si>
+  <si>
+    <t>efforts inhabituels</t>
+  </si>
+  <si>
+    <t>c'est pour la scintigraphie myocardique</t>
+  </si>
+  <si>
+    <t>juste intraveineuse</t>
+  </si>
+  <si>
+    <t>excellent valeur prédictive négative</t>
   </si>
 </sst>
 </file>
@@ -1508,12 +1580,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G374"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="231.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="73.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="100.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.5703125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1539,7 +1615,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1549,8 +1625,17 @@
       <c r="C2" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D2" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1560,8 +1645,14 @@
       <c r="C3" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1571,8 +1662,17 @@
       <c r="C4" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D4" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1582,8 +1682,17 @@
       <c r="C5" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D5" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1593,8 +1702,14 @@
       <c r="C6" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E6" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1604,8 +1719,14 @@
       <c r="C7" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E7" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1615,8 +1736,17 @@
       <c r="C8" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D8" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1626,8 +1756,14 @@
       <c r="C9" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E9" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1636,6 +1772,12 @@
       </c>
       <c r="C10" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1648,6 +1790,15 @@
       <c r="C11" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1659,8 +1810,17 @@
       <c r="C12" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D12" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1670,8 +1830,17 @@
       <c r="C13" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D13" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1680,6 +1849,12 @@
       </c>
       <c r="C14" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1692,8 +1867,17 @@
       <c r="C15" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D15" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1703,8 +1887,14 @@
       <c r="C16" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E16" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1714,8 +1904,17 @@
       <c r="C17" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1725,8 +1924,14 @@
       <c r="C18" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E18" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1736,8 +1941,14 @@
       <c r="C19" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E19" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1747,8 +1958,14 @@
       <c r="C20" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E20" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1758,8 +1975,17 @@
       <c r="C21" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1769,8 +1995,14 @@
       <c r="C22" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E22" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1780,8 +2012,14 @@
       <c r="C23" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E23" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1791,8 +2029,14 @@
       <c r="C24" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E24" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1802,8 +2046,17 @@
       <c r="C25" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1813,8 +2066,14 @@
       <c r="C26" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E26" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1824,8 +2083,14 @@
       <c r="C27" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E27" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1835,8 +2100,14 @@
       <c r="C28" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E28" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1846,8 +2117,17 @@
       <c r="C29" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1857,8 +2137,17 @@
       <c r="C30" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1868,8 +2157,14 @@
       <c r="C31" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E31" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1879,8 +2174,14 @@
       <c r="C32" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E32" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1890,8 +2191,17 @@
       <c r="C33" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1901,8 +2211,17 @@
       <c r="C34" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1912,8 +2231,17 @@
       <c r="C35" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1923,8 +2251,17 @@
       <c r="C36" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1934,8 +2271,14 @@
       <c r="C37" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E37" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1945,8 +2288,14 @@
       <c r="C38" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E38" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1956,8 +2305,17 @@
       <c r="C39" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1967,8 +2325,17 @@
       <c r="C40" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1978,8 +2345,17 @@
       <c r="C41" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1989,8 +2365,17 @@
       <c r="C42" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -2000,8 +2385,14 @@
       <c r="C43" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E43" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -2011,8 +2402,17 @@
       <c r="C44" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -2022,8 +2422,17 @@
       <c r="C45" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -2033,8 +2442,14 @@
       <c r="C46" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E46" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -2044,8 +2459,14 @@
       <c r="C47" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E47" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -2055,8 +2476,14 @@
       <c r="C48" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E48" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -2066,8 +2493,14 @@
       <c r="C49" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E49" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -2077,8 +2510,14 @@
       <c r="C50" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E50" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -2088,8 +2527,14 @@
       <c r="C51" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E51" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -2099,8 +2544,14 @@
       <c r="C52" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E52" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -2110,8 +2561,14 @@
       <c r="C53" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E53" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -2121,8 +2578,14 @@
       <c r="C54" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E54" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -2132,8 +2595,14 @@
       <c r="C55" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E55" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -2143,8 +2612,14 @@
       <c r="C56" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E56" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -2154,8 +2629,14 @@
       <c r="C57" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E57" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -2165,8 +2646,14 @@
       <c r="C58" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E58" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -2176,8 +2663,14 @@
       <c r="C59" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E59" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -2187,8 +2680,14 @@
       <c r="C60" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E60" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -2198,8 +2697,14 @@
       <c r="C61" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E61" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -2209,8 +2714,14 @@
       <c r="C62" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E62" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -2220,8 +2731,14 @@
       <c r="C63" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E63" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -2231,8 +2748,14 @@
       <c r="C64" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E64" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -2242,8 +2765,14 @@
       <c r="C65" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E65" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -2253,8 +2782,14 @@
       <c r="C66" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E66" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -2264,8 +2799,14 @@
       <c r="C67" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E67" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -2275,8 +2816,14 @@
       <c r="C68" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E68" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -2286,8 +2833,14 @@
       <c r="C69" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E69" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -2297,8 +2850,14 @@
       <c r="C70" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E70" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -2308,8 +2867,14 @@
       <c r="C71" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E71" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -2319,8 +2884,14 @@
       <c r="C72" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E72" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -2330,8 +2901,14 @@
       <c r="C73" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E73" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -2341,8 +2918,14 @@
       <c r="C74" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E74" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -2352,8 +2935,14 @@
       <c r="C75" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E75" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -2363,8 +2952,14 @@
       <c r="C76" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E76" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -2374,8 +2969,14 @@
       <c r="C77" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E77" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -2385,8 +2986,14 @@
       <c r="C78" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E78" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -2396,8 +3003,14 @@
       <c r="C79" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E79" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -2407,8 +3020,14 @@
       <c r="C80" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E80" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -2418,8 +3037,14 @@
       <c r="C81" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E81" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -2429,8 +3054,14 @@
       <c r="C82" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E82" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -2440,8 +3071,14 @@
       <c r="C83" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E83" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -2451,8 +3088,14 @@
       <c r="C84" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E84" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -2462,8 +3105,14 @@
       <c r="C85" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E85" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -2473,8 +3122,14 @@
       <c r="C86" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E86" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -2484,8 +3139,14 @@
       <c r="C87" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E87" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -2495,8 +3156,14 @@
       <c r="C88" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E88" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -2506,8 +3173,14 @@
       <c r="C89" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E89" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -2517,8 +3190,14 @@
       <c r="C90" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E90" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -2528,8 +3207,14 @@
       <c r="C91" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E91" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -2539,8 +3224,14 @@
       <c r="C92" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E92" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -2550,8 +3241,14 @@
       <c r="C93" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E93" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -2561,8 +3258,14 @@
       <c r="C94" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E94" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -2572,8 +3275,14 @@
       <c r="C95" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E95" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -2583,8 +3292,14 @@
       <c r="C96" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E96" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -2594,8 +3309,14 @@
       <c r="C97" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E97" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -2605,8 +3326,14 @@
       <c r="C98" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E98" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -2616,8 +3343,14 @@
       <c r="C99" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E99" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -2627,8 +3360,14 @@
       <c r="C100" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E100" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -2638,8 +3377,14 @@
       <c r="C101" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E101" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -2649,8 +3394,14 @@
       <c r="C102" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E102" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -2660,8 +3411,14 @@
       <c r="C103" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E103" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -2671,8 +3428,14 @@
       <c r="C104" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E104" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -2682,8 +3445,14 @@
       <c r="C105" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E105" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -2693,8 +3462,14 @@
       <c r="C106" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E106" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -2704,8 +3479,14 @@
       <c r="C107" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E107" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -2715,8 +3496,14 @@
       <c r="C108" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E108" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -2726,8 +3513,14 @@
       <c r="C109" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E109" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -2737,8 +3530,14 @@
       <c r="C110" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E110" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -2748,8 +3547,14 @@
       <c r="C111" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E111" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -2759,8 +3564,14 @@
       <c r="C112" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E112" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -2770,8 +3581,14 @@
       <c r="C113" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E113" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -2781,16 +3598,28 @@
       <c r="C114" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E114" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E115" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -2800,8 +3629,14 @@
       <c r="C116" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E116" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -2811,8 +3646,14 @@
       <c r="C117" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E117" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -2822,8 +3663,14 @@
       <c r="C118" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E118" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -2833,8 +3680,14 @@
       <c r="C119" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E119" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -2844,8 +3697,14 @@
       <c r="C120" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E120" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -2855,8 +3714,14 @@
       <c r="C121" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E121" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -2866,8 +3731,14 @@
       <c r="C122" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E122" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -2877,8 +3748,14 @@
       <c r="C123" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E123" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -2888,8 +3765,14 @@
       <c r="C124" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E124" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -2899,8 +3782,14 @@
       <c r="C125" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E125" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -2910,8 +3799,14 @@
       <c r="C126" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E126" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -2921,8 +3816,14 @@
       <c r="C127" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E127" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -2932,8 +3833,14 @@
       <c r="C128" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E128" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -2943,8 +3850,14 @@
       <c r="C129" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E129" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -2954,8 +3867,14 @@
       <c r="C130" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E130" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -2965,8 +3884,14 @@
       <c r="C131" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E131" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -2976,8 +3901,14 @@
       <c r="C132" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E132" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -2987,8 +3918,14 @@
       <c r="C133" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E133" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -2998,8 +3935,14 @@
       <c r="C134" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E134" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -3009,8 +3952,14 @@
       <c r="C135" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E135" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -3020,8 +3969,14 @@
       <c r="C136" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E136" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -3031,8 +3986,14 @@
       <c r="C137" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E137" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -3042,8 +4003,14 @@
       <c r="C138" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E138" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -3053,8 +4020,14 @@
       <c r="C139" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E139" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -3064,8 +4037,14 @@
       <c r="C140" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E140" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -3075,8 +4054,14 @@
       <c r="C141" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E141" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -3086,8 +4071,14 @@
       <c r="C142" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E142" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -3097,8 +4088,14 @@
       <c r="C143" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E143" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -3108,8 +4105,14 @@
       <c r="C144" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E144" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -3119,8 +4122,14 @@
       <c r="C145" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E145" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -3130,8 +4139,14 @@
       <c r="C146" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E146" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -3141,8 +4156,14 @@
       <c r="C147" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E147" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -3152,8 +4173,14 @@
       <c r="C148" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E148" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -3163,8 +4190,14 @@
       <c r="C149" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E149" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -3174,8 +4207,14 @@
       <c r="C150" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E150" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -3185,8 +4224,14 @@
       <c r="C151" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E151" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -3196,8 +4241,14 @@
       <c r="C152" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E152" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -3207,8 +4258,14 @@
       <c r="C153" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E153" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -3218,8 +4275,14 @@
       <c r="C154" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E154" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -3229,8 +4292,14 @@
       <c r="C155" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E155" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -3240,8 +4309,14 @@
       <c r="C156" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E156" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -3251,8 +4326,14 @@
       <c r="C157" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E157" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -3262,8 +4343,14 @@
       <c r="C158" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E158" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -3273,8 +4360,14 @@
       <c r="C159" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E159" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -3284,8 +4377,14 @@
       <c r="C160" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E160" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -3295,8 +4394,14 @@
       <c r="C161" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E161" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -3306,8 +4411,14 @@
       <c r="C162" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E162" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -3317,8 +4428,14 @@
       <c r="C163" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E163" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -3328,8 +4445,14 @@
       <c r="C164" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E164" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -3339,8 +4462,14 @@
       <c r="C165" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E165" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -3350,8 +4479,14 @@
       <c r="C166" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E166" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -3361,8 +4496,14 @@
       <c r="C167" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E167" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -3372,8 +4513,14 @@
       <c r="C168" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E168" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -3383,8 +4530,14 @@
       <c r="C169" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E169" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -3394,8 +4547,14 @@
       <c r="C170" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E170" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -3405,8 +4564,14 @@
       <c r="C171" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E171" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -3416,8 +4581,14 @@
       <c r="C172" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E172" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -3427,8 +4598,14 @@
       <c r="C173" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E173" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -3438,8 +4615,14 @@
       <c r="C174" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E174" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -3449,8 +4632,14 @@
       <c r="C175" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E175" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -3460,8 +4649,14 @@
       <c r="C176" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E176" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>176</v>
       </c>
@@ -3471,8 +4666,14 @@
       <c r="C177" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E177" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -3482,8 +4683,14 @@
       <c r="C178" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E178" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>178</v>
       </c>
@@ -3493,8 +4700,14 @@
       <c r="C179" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E179" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -3504,8 +4717,14 @@
       <c r="C180" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E180" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -3515,8 +4734,14 @@
       <c r="C181" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E181" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>181</v>
       </c>
@@ -3526,8 +4751,14 @@
       <c r="C182" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E182" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -3537,8 +4768,14 @@
       <c r="C183" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E183" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>183</v>
       </c>
@@ -3548,8 +4785,14 @@
       <c r="C184" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E184" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>184</v>
       </c>
@@ -3559,8 +4802,14 @@
       <c r="C185" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E185" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>185</v>
       </c>
@@ -3570,8 +4819,14 @@
       <c r="C186" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E186" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>186</v>
       </c>
@@ -3581,8 +4836,14 @@
       <c r="C187" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E187" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>187</v>
       </c>
@@ -3592,8 +4853,14 @@
       <c r="C188" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E188" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>188</v>
       </c>
@@ -3603,8 +4870,14 @@
       <c r="C189" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E189" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>189</v>
       </c>
@@ -3614,8 +4887,14 @@
       <c r="C190" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E190" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>190</v>
       </c>
@@ -3625,8 +4904,14 @@
       <c r="C191" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E191" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>191</v>
       </c>
@@ -3636,8 +4921,14 @@
       <c r="C192" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E192" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>192</v>
       </c>
@@ -3647,8 +4938,14 @@
       <c r="C193" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E193" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>193</v>
       </c>
@@ -3658,8 +4955,14 @@
       <c r="C194" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E194" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>194</v>
       </c>
@@ -3669,8 +4972,14 @@
       <c r="C195" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E195" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>195</v>
       </c>
@@ -3680,8 +4989,14 @@
       <c r="C196" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E196" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>196</v>
       </c>
@@ -3691,8 +5006,14 @@
       <c r="C197" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E197" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>197</v>
       </c>
@@ -3702,8 +5023,14 @@
       <c r="C198" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E198" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>198</v>
       </c>
@@ -3713,8 +5040,14 @@
       <c r="C199" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E199" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>199</v>
       </c>
@@ -3724,8 +5057,14 @@
       <c r="C200" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E200" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>200</v>
       </c>
@@ -3735,8 +5074,14 @@
       <c r="C201" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E201" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>201</v>
       </c>
@@ -3746,8 +5091,14 @@
       <c r="C202" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E202" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>202</v>
       </c>
@@ -3757,8 +5108,14 @@
       <c r="C203" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E203" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>203</v>
       </c>
@@ -3768,8 +5125,14 @@
       <c r="C204" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E204" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>204</v>
       </c>
@@ -3779,8 +5142,14 @@
       <c r="C205" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E205" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>205</v>
       </c>
@@ -3790,8 +5159,14 @@
       <c r="C206" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E206" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>206</v>
       </c>
@@ -3801,8 +5176,14 @@
       <c r="C207" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E207" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>207</v>
       </c>
@@ -3812,8 +5193,14 @@
       <c r="C208" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E208" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>208</v>
       </c>
@@ -3823,8 +5210,14 @@
       <c r="C209" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E209" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>209</v>
       </c>
@@ -3834,8 +5227,14 @@
       <c r="C210" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E210" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>210</v>
       </c>
@@ -3845,8 +5244,14 @@
       <c r="C211" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E211" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>211</v>
       </c>
@@ -3856,8 +5261,14 @@
       <c r="C212" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E212" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>212</v>
       </c>
@@ -3867,8 +5278,14 @@
       <c r="C213" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E213" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>213</v>
       </c>
@@ -3878,8 +5295,14 @@
       <c r="C214" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E214" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>214</v>
       </c>
@@ -3889,8 +5312,14 @@
       <c r="C215" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E215" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>215</v>
       </c>
@@ -3900,8 +5329,14 @@
       <c r="C216" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E216" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>216</v>
       </c>
@@ -3911,8 +5346,14 @@
       <c r="C217" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E217" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>217</v>
       </c>
@@ -3922,8 +5363,14 @@
       <c r="C218" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E218" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>218</v>
       </c>
@@ -3933,8 +5380,14 @@
       <c r="C219" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E219" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>219</v>
       </c>
@@ -3944,8 +5397,14 @@
       <c r="C220" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E220" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>220</v>
       </c>
@@ -3955,8 +5414,14 @@
       <c r="C221" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E221" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>221</v>
       </c>
@@ -3966,8 +5431,14 @@
       <c r="C222" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E222" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>222</v>
       </c>
@@ -3977,8 +5448,14 @@
       <c r="C223" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E223" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>223</v>
       </c>
@@ -3988,8 +5465,14 @@
       <c r="C224" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E224" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>224</v>
       </c>
@@ -3999,8 +5482,14 @@
       <c r="C225" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E225" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>225</v>
       </c>
@@ -4010,8 +5499,14 @@
       <c r="C226" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E226" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>226</v>
       </c>
@@ -4021,8 +5516,14 @@
       <c r="C227" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E227" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>227</v>
       </c>
@@ -4032,8 +5533,14 @@
       <c r="C228" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E228" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>228</v>
       </c>
@@ -4043,8 +5550,14 @@
       <c r="C229" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E229" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>229</v>
       </c>
@@ -4054,8 +5567,14 @@
       <c r="C230" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E230" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>230</v>
       </c>
@@ -4065,8 +5584,14 @@
       <c r="C231" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E231" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>231</v>
       </c>
@@ -4076,8 +5601,14 @@
       <c r="C232" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E232" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>232</v>
       </c>
@@ -4087,8 +5618,14 @@
       <c r="C233" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E233" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>233</v>
       </c>
@@ -4098,8 +5635,14 @@
       <c r="C234" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E234" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>234</v>
       </c>
@@ -4109,8 +5652,14 @@
       <c r="C235" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E235" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F235" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>235</v>
       </c>
@@ -4120,8 +5669,14 @@
       <c r="C236" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E236" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>236</v>
       </c>
@@ -4131,8 +5686,14 @@
       <c r="C237" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E237" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F237" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>237</v>
       </c>
@@ -4142,8 +5703,14 @@
       <c r="C238" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E238" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F238" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>238</v>
       </c>
@@ -4153,8 +5720,14 @@
       <c r="C239" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E239" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>239</v>
       </c>
@@ -4164,8 +5737,14 @@
       <c r="C240" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E240" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>240</v>
       </c>
@@ -4175,8 +5754,14 @@
       <c r="C241" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E241" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F241" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>241</v>
       </c>
@@ -4186,8 +5771,14 @@
       <c r="C242" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E242" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F242" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>242</v>
       </c>
@@ -4197,8 +5788,14 @@
       <c r="C243" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E243" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>243</v>
       </c>
@@ -4208,8 +5805,14 @@
       <c r="C244" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E244" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F244" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>244</v>
       </c>
@@ -4219,8 +5822,14 @@
       <c r="C245" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E245" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F245" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>245</v>
       </c>
@@ -4230,8 +5839,14 @@
       <c r="C246" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E246" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F246" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>246</v>
       </c>
@@ -4241,8 +5856,14 @@
       <c r="C247" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E247" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F247" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>247</v>
       </c>
@@ -4252,8 +5873,14 @@
       <c r="C248" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E248" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F248" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>248</v>
       </c>
@@ -4263,8 +5890,14 @@
       <c r="C249" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E249" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F249" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>249</v>
       </c>
@@ -4274,8 +5907,14 @@
       <c r="C250" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E250" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>250</v>
       </c>
@@ -4285,8 +5924,14 @@
       <c r="C251" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E251" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>251</v>
       </c>
@@ -4296,8 +5941,14 @@
       <c r="C252" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E252" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>252</v>
       </c>
@@ -4307,8 +5958,14 @@
       <c r="C253" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E253" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>253</v>
       </c>
@@ -4318,8 +5975,14 @@
       <c r="C254" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E254" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F254" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>254</v>
       </c>
@@ -4329,8 +5992,14 @@
       <c r="C255" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E255" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F255" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>255</v>
       </c>
@@ -4340,8 +6009,14 @@
       <c r="C256" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E256" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F256" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>256</v>
       </c>
@@ -4351,8 +6026,14 @@
       <c r="C257" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E257" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F257" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>257</v>
       </c>
@@ -4362,8 +6043,14 @@
       <c r="C258" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E258" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F258" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>258</v>
       </c>
@@ -4373,8 +6060,14 @@
       <c r="C259" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E259" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F259" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>259</v>
       </c>
@@ -4384,8 +6077,14 @@
       <c r="C260" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E260" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F260" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>260</v>
       </c>
@@ -4395,8 +6094,14 @@
       <c r="C261" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E261" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F261" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>261</v>
       </c>
@@ -4406,8 +6111,14 @@
       <c r="C262" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E262" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F262" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>262</v>
       </c>
@@ -4417,8 +6128,14 @@
       <c r="C263" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E263" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F263" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>263</v>
       </c>
@@ -4428,8 +6145,14 @@
       <c r="C264" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E264" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F264" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>264</v>
       </c>
@@ -4439,8 +6162,14 @@
       <c r="C265" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E265" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>265</v>
       </c>
@@ -4450,8 +6179,14 @@
       <c r="C266" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E266" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F266" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>266</v>
       </c>
@@ -4461,8 +6196,14 @@
       <c r="C267" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E267" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F267" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>267</v>
       </c>
@@ -4472,8 +6213,14 @@
       <c r="C268" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E268" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F268" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>268</v>
       </c>
@@ -4483,8 +6230,14 @@
       <c r="C269" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E269" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F269" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>269</v>
       </c>
@@ -4494,8 +6247,14 @@
       <c r="C270" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E270" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>270</v>
       </c>
@@ -4505,8 +6264,14 @@
       <c r="C271" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E271" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F271" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>271</v>
       </c>
@@ -4516,8 +6281,14 @@
       <c r="C272" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E272" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F272" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>272</v>
       </c>
@@ -4527,8 +6298,14 @@
       <c r="C273" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E273" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F273" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>273</v>
       </c>
@@ -4538,8 +6315,14 @@
       <c r="C274" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E274" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F274" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>274</v>
       </c>
@@ -4549,8 +6332,14 @@
       <c r="C275" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E275" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F275" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>275</v>
       </c>
@@ -4560,8 +6349,14 @@
       <c r="C276" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E276" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F276" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>276</v>
       </c>
@@ -4571,8 +6366,14 @@
       <c r="C277" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E277" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F277" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>277</v>
       </c>
@@ -4582,8 +6383,14 @@
       <c r="C278" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E278" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F278" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>278</v>
       </c>
@@ -4593,8 +6400,14 @@
       <c r="C279" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E279" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F279" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>279</v>
       </c>
@@ -4604,8 +6417,14 @@
       <c r="C280" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E280" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F280" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>280</v>
       </c>
@@ -4615,8 +6434,14 @@
       <c r="C281" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E281" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F281" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>281</v>
       </c>
@@ -4626,8 +6451,14 @@
       <c r="C282" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E282" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F282" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>282</v>
       </c>
@@ -4637,8 +6468,14 @@
       <c r="C283" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E283" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F283" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>283</v>
       </c>
@@ -4648,8 +6485,14 @@
       <c r="C284" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E284" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F284" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>284</v>
       </c>
@@ -4659,8 +6502,14 @@
       <c r="C285" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E285" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F285" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>285</v>
       </c>
@@ -4670,8 +6519,14 @@
       <c r="C286" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E286" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F286" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>286</v>
       </c>
@@ -4681,8 +6536,14 @@
       <c r="C287" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E287" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F287" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>287</v>
       </c>
@@ -4692,8 +6553,14 @@
       <c r="C288" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E288" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F288" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>288</v>
       </c>
@@ -4703,8 +6570,14 @@
       <c r="C289" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E289" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F289" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>289</v>
       </c>
@@ -4714,8 +6587,14 @@
       <c r="C290" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E290" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F290" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>290</v>
       </c>
@@ -4725,8 +6604,14 @@
       <c r="C291" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E291" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F291" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>291</v>
       </c>
@@ -4736,8 +6621,14 @@
       <c r="C292" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E292" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F292" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>292</v>
       </c>
@@ -4747,8 +6638,14 @@
       <c r="C293" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E293" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F293" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>293</v>
       </c>
@@ -4758,8 +6655,14 @@
       <c r="C294" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E294" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F294" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>294</v>
       </c>
@@ -4769,8 +6672,14 @@
       <c r="C295" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E295" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F295" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>295</v>
       </c>
@@ -4780,8 +6689,14 @@
       <c r="C296" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E296" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F296" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>296</v>
       </c>
@@ -4791,8 +6706,14 @@
       <c r="C297" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E297" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F297" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>297</v>
       </c>
@@ -4802,8 +6723,14 @@
       <c r="C298" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E298" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F298" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>298</v>
       </c>
@@ -4813,8 +6740,14 @@
       <c r="C299" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E299" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F299" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>299</v>
       </c>
@@ -4824,8 +6757,14 @@
       <c r="C300" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E300" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F300" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>300</v>
       </c>
@@ -4835,8 +6774,14 @@
       <c r="C301" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E301" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F301" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>301</v>
       </c>
@@ -4846,8 +6791,14 @@
       <c r="C302" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E302" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F302" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>302</v>
       </c>
@@ -4857,8 +6808,14 @@
       <c r="C303" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E303" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F303" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>303</v>
       </c>
@@ -4868,8 +6825,14 @@
       <c r="C304" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E304" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F304" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>304</v>
       </c>
@@ -4879,8 +6842,14 @@
       <c r="C305" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E305" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F305" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>305</v>
       </c>
@@ -4890,8 +6859,14 @@
       <c r="C306" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E306" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F306" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>306</v>
       </c>
@@ -4901,8 +6876,14 @@
       <c r="C307" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E307" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F307" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>307</v>
       </c>
@@ -4912,8 +6893,14 @@
       <c r="C308" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E308" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F308" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>308</v>
       </c>
@@ -4923,8 +6910,14 @@
       <c r="C309" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E309" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F309" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>309</v>
       </c>
@@ -4934,8 +6927,14 @@
       <c r="C310" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E310" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F310" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>310</v>
       </c>
@@ -4945,8 +6944,14 @@
       <c r="C311" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E311" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F311" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>311</v>
       </c>
@@ -4956,8 +6961,14 @@
       <c r="C312" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E312" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F312" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>312</v>
       </c>
@@ -4967,8 +6978,14 @@
       <c r="C313" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E313" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F313" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>313</v>
       </c>
@@ -4978,8 +6995,14 @@
       <c r="C314" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E314" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F314" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>314</v>
       </c>
@@ -4989,8 +7012,14 @@
       <c r="C315" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E315" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F315" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>315</v>
       </c>
@@ -5000,8 +7029,14 @@
       <c r="C316" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E316" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F316" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>316</v>
       </c>
@@ -5011,8 +7046,14 @@
       <c r="C317" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E317" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F317" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>317</v>
       </c>
@@ -5022,8 +7063,14 @@
       <c r="C318" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E318" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F318" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>318</v>
       </c>
@@ -5033,8 +7080,14 @@
       <c r="C319" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E319" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F319" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>319</v>
       </c>
@@ -5044,8 +7097,14 @@
       <c r="C320" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E320" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F320" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>320</v>
       </c>
@@ -5055,8 +7114,14 @@
       <c r="C321" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E321" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F321" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>321</v>
       </c>
@@ -5066,8 +7131,14 @@
       <c r="C322" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E322" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F322" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>322</v>
       </c>
@@ -5077,8 +7148,14 @@
       <c r="C323" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E323" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F323" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>323</v>
       </c>
@@ -5088,8 +7165,14 @@
       <c r="C324" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E324" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F324" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <v>324</v>
       </c>
@@ -5099,8 +7182,14 @@
       <c r="C325" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E325" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F325" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <v>325</v>
       </c>
@@ -5110,8 +7199,14 @@
       <c r="C326" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E326" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F326" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>326</v>
       </c>
@@ -5121,8 +7216,14 @@
       <c r="C327" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E327" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F327" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>327</v>
       </c>
@@ -5132,8 +7233,14 @@
       <c r="C328" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E328" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F328" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>328</v>
       </c>
@@ -5143,8 +7250,14 @@
       <c r="C329" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E329" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F329" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <v>329</v>
       </c>
@@ -5154,8 +7267,14 @@
       <c r="C330" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E330" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F330" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
         <v>330</v>
       </c>
@@ -5165,8 +7284,14 @@
       <c r="C331" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E331" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F331" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <v>331</v>
       </c>
@@ -5176,8 +7301,14 @@
       <c r="C332" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E332" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F332" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <v>332</v>
       </c>
@@ -5187,8 +7318,14 @@
       <c r="C333" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E333" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F333" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>333</v>
       </c>
@@ -5198,8 +7335,14 @@
       <c r="C334" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E334" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F334" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>334</v>
       </c>
@@ -5209,8 +7352,14 @@
       <c r="C335" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E335" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F335" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>335</v>
       </c>
@@ -5220,8 +7369,14 @@
       <c r="C336" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E336" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F336" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>336</v>
       </c>
@@ -5231,8 +7386,14 @@
       <c r="C337" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E337" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F337" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>337</v>
       </c>
@@ -5242,8 +7403,14 @@
       <c r="C338" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E338" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F338" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>338</v>
       </c>
@@ -5253,8 +7420,14 @@
       <c r="C339" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E339" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F339" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>339</v>
       </c>
@@ -5264,8 +7437,14 @@
       <c r="C340" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E340" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F340" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>340</v>
       </c>
@@ -5275,8 +7454,14 @@
       <c r="C341" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E341" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F341" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>341</v>
       </c>
@@ -5286,8 +7471,14 @@
       <c r="C342" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E342" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F342" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>342</v>
       </c>
@@ -5297,8 +7488,14 @@
       <c r="C343" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E343" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F343" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>343</v>
       </c>
@@ -5308,8 +7505,14 @@
       <c r="C344" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E344" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F344" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>344</v>
       </c>
@@ -5319,8 +7522,14 @@
       <c r="C345" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E345" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F345" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>345</v>
       </c>
@@ -5330,8 +7539,14 @@
       <c r="C346" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E346" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F346" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>346</v>
       </c>
@@ -5341,8 +7556,14 @@
       <c r="C347" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E347" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F347" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>347</v>
       </c>
@@ -5352,8 +7573,14 @@
       <c r="C348" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E348" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F348" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>348</v>
       </c>
@@ -5363,8 +7590,14 @@
       <c r="C349" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E349" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F349" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>349</v>
       </c>
@@ -5374,8 +7607,14 @@
       <c r="C350" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E350" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F350" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <v>350</v>
       </c>
@@ -5385,8 +7624,14 @@
       <c r="C351" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E351" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F351" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>351</v>
       </c>
@@ -5396,8 +7641,14 @@
       <c r="C352" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E352" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F352" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>352</v>
       </c>
@@ -5407,8 +7658,14 @@
       <c r="C353" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E353" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F353" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>353</v>
       </c>
@@ -5418,8 +7675,14 @@
       <c r="C354" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E354" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F354" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>354</v>
       </c>
@@ -5429,8 +7692,14 @@
       <c r="C355" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E355" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F355" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>355</v>
       </c>
@@ -5440,8 +7709,14 @@
       <c r="C356" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E356" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F356" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <v>356</v>
       </c>
@@ -5451,8 +7726,14 @@
       <c r="C357" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E357" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F357" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>357</v>
       </c>
@@ -5462,8 +7743,14 @@
       <c r="C358" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E358" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F358" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <v>358</v>
       </c>
@@ -5473,8 +7760,14 @@
       <c r="C359" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E359" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F359" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>359</v>
       </c>
@@ -5484,8 +7777,14 @@
       <c r="C360" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E360" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F360" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
         <v>360</v>
       </c>
@@ -5495,8 +7794,14 @@
       <c r="C361" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E361" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F361" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <v>361</v>
       </c>
@@ -5506,8 +7811,14 @@
       <c r="C362" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E362" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F362" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <v>362</v>
       </c>
@@ -5517,8 +7828,14 @@
       <c r="C363" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E363" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F363" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <v>363</v>
       </c>
@@ -5528,8 +7845,14 @@
       <c r="C364" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E364" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F364" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>364</v>
       </c>
@@ -5539,8 +7862,14 @@
       <c r="C365" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E365" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F365" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
         <v>365</v>
       </c>
@@ -5550,8 +7879,14 @@
       <c r="C366" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E366" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F366" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
         <v>366</v>
       </c>
@@ -5561,8 +7896,14 @@
       <c r="C367" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E367" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F367" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <v>367</v>
       </c>
@@ -5572,8 +7913,14 @@
       <c r="C368" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E368" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F368" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <v>368</v>
       </c>
@@ -5583,8 +7930,14 @@
       <c r="C369" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E369" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F369" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>369</v>
       </c>
@@ -5594,8 +7947,14 @@
       <c r="C370" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E370" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F370" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
         <v>370</v>
       </c>
@@ -5605,8 +7964,14 @@
       <c r="C371" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E371" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F371" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <v>371</v>
       </c>
@@ -5616,8 +7981,14 @@
       <c r="C372" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E372" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F372" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <v>372</v>
       </c>
@@ -5627,8 +7998,14 @@
       <c r="C373" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E373" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F373" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <v>373</v>
       </c>
@@ -5637,6 +8014,12 @@
       </c>
       <c r="C374" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="E374" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F374" s="1" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>
